--- a/diseases/d165/2005-2009.xlsx
+++ b/diseases/d165/2005-2009.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1317,6 +1322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1858,6 +1868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2006,6 +2021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2547,6 +2567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2695,6 +2720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3236,6 +3266,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3384,6 +3419,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3925,6 +3965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4073,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4614,6 +4664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4762,6 +4817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5303,6 +5363,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5451,6 +5516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5992,6 +6062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6140,6 +6215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6681,6 +6761,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6829,6 +6914,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7370,6 +7460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7518,6 +7613,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8059,6 +8159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8207,6 +8312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8748,6 +8858,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8896,6 +9011,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9437,6 +9557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9585,6 +9710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10126,6 +10256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10274,6 +10409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10815,6 +10955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10963,6 +11108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11504,6 +11654,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11652,6 +11807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12193,6 +12353,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12341,6 +12506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12882,6 +13052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13030,6 +13205,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13571,6 +13751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13719,6 +13904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14260,6 +14450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14408,6 +14603,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14949,6 +15149,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15097,6 +15302,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15638,6 +15848,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15786,6 +16001,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16327,6 +16547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16475,6 +16700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17016,6 +17246,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17164,6 +17399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17705,6 +17945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17853,6 +18098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18394,6 +18644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18542,6 +18797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19083,6 +19343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19231,6 +19496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19772,6 +20042,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19920,6 +20195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20461,6 +20741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20609,6 +20894,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21150,6 +21440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21298,6 +21593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21839,6 +22139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21987,6 +22292,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22528,6 +22838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22676,6 +22991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23217,6 +23537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23365,6 +23690,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23906,6 +24236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24054,6 +24389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24595,6 +24935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24743,6 +25088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25284,6 +25634,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25432,6 +25787,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25973,6 +26333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26121,6 +26486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26662,6 +27032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26810,6 +27185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27351,6 +27731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27499,6 +27884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28040,6 +28430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28188,6 +28583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28729,6 +29129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28877,6 +29282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29418,6 +29828,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29566,6 +29981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30107,6 +30527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30255,6 +30680,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30796,6 +31226,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30944,6 +31379,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31485,6 +31925,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31633,6 +32078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32174,6 +32624,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32322,6 +32777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32863,6 +33323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33011,6 +33476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33552,6 +34022,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33700,6 +34175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34241,6 +34721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34389,6 +34874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34930,6 +35420,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35078,6 +35573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35619,6 +36119,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35767,6 +36272,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36308,6 +36818,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36456,6 +36971,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36997,6 +37517,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37145,6 +37670,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37686,6 +38216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37834,6 +38369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38375,6 +38915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38523,6 +39068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39064,6 +39614,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39212,6 +39767,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39753,6 +40313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39901,6 +40466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40442,6 +41012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40590,6 +41165,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41131,6 +41711,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41279,6 +41864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41820,6 +42410,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41966,6 +42561,11 @@
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
